--- a/config/_TableConfig/#Combat.Campaign-战役-7.xlsx
+++ b/config/_TableConfig/#Combat.Campaign-战役-7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26490" windowHeight="13000"/>
+    <workbookView windowHeight="15120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -141,7 +141,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -149,14 +149,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -164,7 +164,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +172,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -180,7 +180,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -188,7 +188,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,14 +196,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -211,7 +211,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -219,7 +219,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -227,14 +227,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -242,42 +242,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -766,55 +766,55 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1084,7 +1084,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -1504,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="9">
         <v>60005</v>
@@ -1513,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="8">
         <v>60005</v>
@@ -1522,13 +1522,13 @@
         <v>1</v>
       </c>
       <c r="M9" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N9" s="9">
         <v>60005</v>
       </c>
       <c r="O9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="9">
         <v>5</v>

--- a/config/_TableConfig/#Combat.Campaign-战役-7.xlsx
+++ b/config/_TableConfig/#Combat.Campaign-战役-7.xlsx
@@ -50,10 +50,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>map,string,(array,Combat.SquadStance)</t>
-  </si>
-  <si>
-    <t>Combat.SquadStance</t>
+    <t>map,string,(array,Combat.SquadFormation)</t>
+  </si>
+  <si>
+    <t>Combat.SquadFormation</t>
   </si>
   <si>
     <t>row</t>
@@ -743,10 +743,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1159,36 +1168,36 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1" t="s">
+      <c r="O3" s="4"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1" t="s">
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="5"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
@@ -1321,241 +1330,247 @@
       </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7">
         <v>70001</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="9">
         <v>65006</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="9">
         <v>2</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="9">
         <v>3</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="10">
         <v>65002</v>
       </c>
-      <c r="I6" s="7">
-        <v>1</v>
-      </c>
-      <c r="J6" s="7">
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
         <v>3</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="9">
         <v>65002</v>
       </c>
-      <c r="L6" s="6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="6">
+      <c r="L6" s="9">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9">
         <v>4</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="10">
         <v>65004</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="10">
         <v>3</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="10">
         <v>3</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="9">
         <v>65004</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="9">
         <v>3</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="9">
         <v>4</v>
       </c>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>65005</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11">
         <v>4</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="12">
         <v>65001</v>
       </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
+      <c r="I7" s="12">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12">
         <v>3</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="11">
         <v>65001</v>
       </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8">
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="11">
         <v>5</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="12">
         <v>65003</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="12">
         <v>3</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="12">
         <v>3</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="11">
         <v>65003</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="11">
         <v>3</v>
       </c>
-      <c r="S7" s="8">
+      <c r="S7" s="11">
         <v>4</v>
       </c>
-      <c r="T7" s="9">
+      <c r="T7" s="12">
         <v>65003</v>
       </c>
-      <c r="U7" s="9">
+      <c r="U7" s="12">
         <v>3</v>
       </c>
-      <c r="V7" s="9">
+      <c r="V7" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7">
         <v>71001</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="9">
         <v>10001</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="9">
         <v>2</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="9">
         <v>3</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="10">
         <v>60002</v>
       </c>
-      <c r="I8" s="7">
-        <v>1</v>
-      </c>
-      <c r="J8" s="7">
+      <c r="I8" s="10">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10">
         <v>3</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="9">
         <v>60002</v>
       </c>
-      <c r="L8" s="6">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6">
+      <c r="L8" s="9">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9">
         <v>5</v>
       </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>10002</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12">
         <v>60005</v>
       </c>
-      <c r="I9" s="9">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12">
         <v>3</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="11">
         <v>60005</v>
       </c>
-      <c r="L9" s="8">
-        <v>1</v>
-      </c>
-      <c r="M9" s="8">
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
         <v>5</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="12">
         <v>60005</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="12">
         <v>2</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="12">
         <v>5</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="11">
         <v>60003</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="11">
         <v>3</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="11">
         <v>2</v>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="12">
         <v>60003</v>
       </c>
-      <c r="U9" s="9">
+      <c r="U9" s="12">
         <v>3</v>
       </c>
-      <c r="V9" s="9">
+      <c r="V9" s="12">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="8">
     <mergeCell ref="D1:V1"/>
     <mergeCell ref="D2:V2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T3:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
